--- a/data/demo/documents/D-03_electricity.xlsx
+++ b/data/demo/documents/D-03_electricity.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Electricity Bill — China Southern Power Grid</t>
+          <t>Electricity Bill — Austin Energy</t>
         </is>
       </c>
     </row>
@@ -431,7 +431,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Meridian Electronics Manufacturing Co., Ltd.</t>
+          <t>Meridian Electronics Manufacturing, Inc.</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>amount_cny</t>
+          <t>amount_usd</t>
         </is>
       </c>
     </row>
@@ -474,7 +474,7 @@
         <v>1250000</v>
       </c>
       <c r="C5" t="n">
-        <v>980000</v>
+        <v>152000</v>
       </c>
     </row>
   </sheetData>
